--- a/02_DIA_inicio_2026_analisis_assets/rbd_9730_colegio-antu_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9730_colegio-antu_nt2_rubricas.xlsx
@@ -1932,13 +1932,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E34F201A-8898-4D78-94A9-28DAA0D76243}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A47E8C9-D0A7-4C98-85DE-0BB4E65165B2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BD3DF7E-F992-4C7E-B698-B72D5F36771B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1091C97A-D959-481A-B883-45BBBABA3D55}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2078989B-2C7F-4438-986A-56005DAC5660}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8005D170-B65B-46B0-84D0-E76ABD7973F9}"/>
 </file>